--- a/data/trans_dic/P42C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -516,39 +516,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -579,21 +569,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -608,9 +583,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -625,17 +597,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,21 +621,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,95%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>39,36%</t>
         </is>
@@ -678,47 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,2; 33,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,9; 26,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,2; 53,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,88; 33,18</t>
+          <t>21,2; 33,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,71; 28,0</t>
+          <t>15,9; 26,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 53,32</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,88; 33,18</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15,71; 28,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26,7; 53,32</t>
+          <t>26,2; 53,46</t>
         </is>
       </c>
     </row>
@@ -735,17 +677,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -759,21 +701,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>29,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21,31%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22,41%</t>
         </is>
@@ -788,47 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,87; 34,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,83; 25,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,47; 31,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,39; 33,86</t>
+          <t>25,87; 34,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 25,42</t>
+          <t>17,83; 25,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 32,0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>25,39; 33,86</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17,94; 25,42</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10,5; 32,0</t>
+          <t>10,47; 31,85</t>
         </is>
       </c>
     </row>
@@ -845,17 +757,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,21 +781,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25,9%</t>
         </is>
@@ -898,47 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,75; 32,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,51; 24,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,02; 30,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,96; 32,37</t>
+          <t>24,75; 32,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 24,31</t>
+          <t>17,51; 24,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,98; 30,09</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>24,96; 32,37</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17,07; 24,31</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21,98; 30,09</t>
+          <t>22,02; 30,07</t>
         </is>
       </c>
     </row>
@@ -955,17 +837,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,21 +861,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>30,21%</t>
         </is>
@@ -1008,47 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,57; 30,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,25; 17,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,5; 34,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,87; 30,93</t>
+          <t>22,57; 30,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,63; 17,57</t>
+          <t>11,25; 17,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,86; 34,43</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22,87; 30,93</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11,63; 17,57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22,86; 34,43</t>
+          <t>23,5; 34,39</t>
         </is>
       </c>
     </row>
@@ -1065,17 +917,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,21 +941,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>21,21%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>21,21%</t>
         </is>
@@ -1118,47 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,66; 21,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,3; 16,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,11; 24,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 20,8</t>
+          <t>12,66; 21,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 16,1</t>
+          <t>9,3; 16,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,14; 24,54</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,37; 20,8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9,0; 16,1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18,14; 24,54</t>
+          <t>18,11; 24,57</t>
         </is>
       </c>
     </row>
@@ -1175,17 +997,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1199,21 +1021,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,87%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>16,87%</t>
         </is>
@@ -1228,47 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,03; 20,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,98; 13,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,83; 20,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 20,3</t>
+          <t>11,03; 20,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 13,46</t>
+          <t>5,98; 13,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,84; 19,89</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>10,86; 20,3</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>6,29; 13,46</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>13,84; 19,89</t>
+          <t>13,83; 20,56</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1077,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1309,21 +1101,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11,7%</t>
         </is>
@@ -1338,47 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,11; 17,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,6; 6,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,12; 14,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,69; 17,33</t>
+          <t>7,11; 17,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,05</t>
+          <t>0,6; 6,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,69</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>7,69; 17,33</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 6,05</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>9,02; 14,69</t>
+          <t>9,12; 14,96</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1157,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1419,21 +1181,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>23,2%</t>
         </is>
@@ -1448,47 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,97; 25,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,06; 16,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20,01; 25,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,3; 25,73</t>
+          <t>21,97; 25,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,25; 17,01</t>
+          <t>14,06; 16,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,44; 25,25</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>22,3; 25,73</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14,25; 17,01</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>20,44; 25,25</t>
+          <t>20,01; 25,0</t>
         </is>
       </c>
     </row>
@@ -1500,13 +1232,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
@@ -1524,7 +1255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1535,39 +1266,29 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya última consulta ginecológica fue en un centro privado</t>
+          <t>Población cuya última consulta ginecológica fue en un centro privado (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1598,21 +1319,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -1627,9 +1333,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1644,17 +1347,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1668,21 +1371,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1697,17 +1385,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62703</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45199</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1721,21 +1409,6 @@
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36458</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62703</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>45199</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>36458</t>
         </is>
@@ -1750,47 +1423,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49312; 76867</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34315; 57642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24268; 49524</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48581; 77204</t>
+          <t>49312; 76867</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33905; 60435</t>
+          <t>34315; 57642</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24733; 49386</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>48581; 77204</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>33905; 60435</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24733; 49386</t>
+          <t>24268; 49524</t>
         </is>
       </c>
     </row>
@@ -1807,17 +1465,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>135</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1831,21 +1489,6 @@
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
@@ -1860,17 +1503,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145438</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98683</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1884,21 +1527,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>64391</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>145438</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>98683</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64391</t>
         </is>
@@ -1913,47 +1541,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>126490; 170005</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82538; 116566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30087; 91515</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124168; 165570</t>
+          <t>126490; 170005</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83088; 117697</t>
+          <t>82538; 116566</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30175; 91955</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>124168; 165570</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>83088; 117697</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>30175; 91955</t>
+          <t>30087; 91515</t>
         </is>
       </c>
     </row>
@@ -1970,17 +1583,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1994,21 +1607,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>120</t>
         </is>
@@ -2023,17 +1621,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176081</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119213</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>79297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2047,21 +1645,6 @@
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79297</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>176081</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>119213</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>79297</t>
         </is>
@@ -2076,47 +1659,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>153183; 198804</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>102117; 139994</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>67420; 92060</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154475; 200309</t>
+          <t>153183; 198804</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>99534; 141757</t>
+          <t>102117; 139994</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67275; 92102</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>154475; 200309</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>99534; 141757</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>67275; 92102</t>
+          <t>67420; 92060</t>
         </is>
       </c>
     </row>
@@ -2133,17 +1701,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2157,21 +1725,6 @@
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>226</t>
         </is>
@@ -2186,17 +1739,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143356</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81492</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2210,21 +1763,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>136657</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>143356</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>81492</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>136657</t>
         </is>
@@ -2239,47 +1777,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>121329; 166400</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64702; 98690</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>106321; 155576</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122902; 166252</t>
+          <t>121329; 166400</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66930; 101084</t>
+          <t>64702; 98690</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>103436; 155774</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>122902; 166252</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>66930; 101084</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>103436; 155774</t>
+          <t>106321; 155576</t>
         </is>
       </c>
     </row>
@@ -2296,17 +1819,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2320,21 +1843,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>133</t>
         </is>
@@ -2349,17 +1857,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64547</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53981</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2373,21 +1881,6 @@
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75860</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>64547</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>53981</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>75860</t>
         </is>
@@ -2402,47 +1895,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49461; 82364</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40227; 69744</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64795; 87908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48306; 81239</t>
+          <t>49461; 82364</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38916; 69612</t>
+          <t>40227; 69744</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64887; 87773</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>48306; 81239</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>38916; 69612</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>64887; 87773</t>
+          <t>64795; 87908</t>
         </is>
       </c>
     </row>
@@ -2459,17 +1937,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2483,21 +1961,6 @@
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
@@ -2512,17 +1975,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38812</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45670</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2536,21 +1999,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>45670</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>38812</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>26331</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>45670</t>
         </is>
@@ -2565,47 +2013,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28398; 51958</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16876; 37808</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37445; 55677</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27963; 52290</t>
+          <t>28398; 51958</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17732; 37947</t>
+          <t>16876; 37808</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37485; 53848</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>27963; 52290</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17732; 37947</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>37485; 53848</t>
+          <t>37445; 55677</t>
         </is>
       </c>
     </row>
@@ -2622,17 +2055,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2646,21 +2079,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -2675,17 +2093,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24738</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2699,21 +2117,6 @@
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>29003</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>24738</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>29003</t>
         </is>
@@ -2728,47 +2131,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15206; 37144</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1343; 14208</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22590; 37081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16453; 37062</t>
+          <t>15206; 37144</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1340; 13617</t>
+          <t>1343; 14208</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22347; 36396</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>16453; 37062</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1340; 13617</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>22347; 36396</t>
+          <t>22590; 37081</t>
         </is>
       </c>
     </row>
@@ -2785,17 +2173,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>404</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2809,21 +2197,6 @@
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>711</t>
         </is>
@@ -2838,17 +2211,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655675</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429531</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467337</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2862,21 +2235,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>467337</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>655675</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>429531</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>467337</t>
         </is>
@@ -2891,47 +2249,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>601929; 701351</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>390425; 470981</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>403168; 503641</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>611083; 705108</t>
+          <t>601929; 701351</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>395628; 472258</t>
+          <t>390425; 470981</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>411727; 508802</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>611083; 705108</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>395628; 472258</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>411727; 508802</t>
+          <t>403168; 503641</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2286,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -2951,7 +2294,6 @@
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A25:A27"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A22:A24"/>

--- a/data/trans_dic/P42C_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P42C_R-Edad-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,2; 33,04</t>
+          <t>21,24; 32,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,9; 26,7</t>
+          <t>15,96; 26,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,2; 53,46</t>
+          <t>23,6; 48,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,2; 33,04</t>
+          <t>21,24; 32,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,9; 26,7</t>
+          <t>15,96; 26,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,2; 53,46</t>
+          <t>23,6; 48,81</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,87; 34,77</t>
+          <t>25,69; 34,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 25,17</t>
+          <t>17,56; 25,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 31,85</t>
+          <t>23,65; 36,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,87; 34,77</t>
+          <t>25,69; 34,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,83; 25,17</t>
+          <t>17,56; 25,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,47; 31,85</t>
+          <t>23,65; 36,35</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,75; 32,12</t>
+          <t>24,9; 32,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 24,0</t>
+          <t>17,0; 23,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 30,07</t>
+          <t>21,32; 28,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,75; 32,12</t>
+          <t>24,9; 32,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,51; 24,0</t>
+          <t>17,0; 23,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 30,07</t>
+          <t>21,32; 28,97</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,57; 30,96</t>
+          <t>22,85; 30,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 17,16</t>
+          <t>11,48; 17,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,5; 34,39</t>
+          <t>29,72; 36,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,57; 30,96</t>
+          <t>22,85; 30,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 17,16</t>
+          <t>11,48; 17,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,5; 34,39</t>
+          <t>29,72; 36,49</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,08</t>
+          <t>12,63; 20,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 16,13</t>
+          <t>9,36; 16,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,11; 24,57</t>
+          <t>18,37; 24,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,08</t>
+          <t>12,63; 20,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,3; 16,13</t>
+          <t>9,36; 16,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,11; 24,57</t>
+          <t>18,37; 24,78</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 20,17</t>
+          <t>10,58; 20,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,41</t>
+          <t>6,16; 13,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,83; 20,56</t>
+          <t>14,18; 20,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,03; 20,17</t>
+          <t>10,58; 20,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,41</t>
+          <t>6,16; 13,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,83; 20,56</t>
+          <t>14,18; 20,65</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 17,36</t>
+          <t>7,49; 17,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,31</t>
+          <t>0,6; 5,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,96</t>
+          <t>9,08; 14,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 17,36</t>
+          <t>7,49; 17,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,31</t>
+          <t>0,6; 5,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 14,96</t>
+          <t>9,08; 14,89</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,97; 25,6</t>
+          <t>22,29; 25,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,96</t>
+          <t>14,19; 16,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,01; 25,0</t>
+          <t>22,61; 26,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,97; 25,6</t>
+          <t>22,29; 25,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,06; 16,96</t>
+          <t>14,19; 16,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,01; 25,0</t>
+          <t>22,61; 26,0</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36458</t>
+          <t>37654</t>
         </is>
       </c>
     </row>
@@ -1423,32 +1423,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>49312; 76867</t>
+          <t>49412; 75870</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34315; 57642</t>
+          <t>34458; 57731</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24268; 49524</t>
+          <t>25329; 52393</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49312; 76867</t>
+          <t>49412; 75870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34315; 57642</t>
+          <t>34458; 57731</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24268; 49524</t>
+          <t>25329; 52393</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>71205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>71205</t>
         </is>
       </c>
     </row>
@@ -1541,32 +1541,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126490; 170005</t>
+          <t>125598; 166419</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82538; 116566</t>
+          <t>81305; 116803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30087; 91515</t>
+          <t>57366; 88169</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>126490; 170005</t>
+          <t>125598; 166419</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82538; 116566</t>
+          <t>81305; 116803</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30087; 91515</t>
+          <t>57366; 88169</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79297</t>
+          <t>87345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79297</t>
+          <t>87345</t>
         </is>
       </c>
     </row>
@@ -1659,32 +1659,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>153183; 198804</t>
+          <t>154111; 200942</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102117; 139994</t>
+          <t>99159; 138588</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67420; 92060</t>
+          <t>73777; 100249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>153183; 198804</t>
+          <t>154111; 200942</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>102117; 139994</t>
+          <t>99159; 138588</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67420; 92060</t>
+          <t>73777; 100249</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136657</t>
+          <t>148766</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>136657</t>
+          <t>148766</t>
         </is>
       </c>
     </row>
@@ -1777,32 +1777,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121329; 166400</t>
+          <t>122784; 165732</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64702; 98690</t>
+          <t>66068; 100572</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>106321; 155576</t>
+          <t>134036; 164600</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121329; 166400</t>
+          <t>122784; 165732</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>64702; 98690</t>
+          <t>66068; 100572</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>106321; 155576</t>
+          <t>134036; 164600</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75860</t>
+          <t>84930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75860</t>
+          <t>84930</t>
         </is>
       </c>
     </row>
@@ -1895,32 +1895,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49461; 82364</t>
+          <t>49324; 81911</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40227; 69744</t>
+          <t>40488; 69970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64795; 87908</t>
+          <t>72919; 98333</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49461; 82364</t>
+          <t>49324; 81911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>40227; 69744</t>
+          <t>40488; 69970</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>64795; 87908</t>
+          <t>72919; 98333</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45670</t>
+          <t>50613</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45670</t>
+          <t>50613</t>
         </is>
       </c>
     </row>
@@ -2013,32 +2013,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28398; 51958</t>
+          <t>27239; 52436</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16876; 37808</t>
+          <t>17373; 38974</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37445; 55677</t>
+          <t>41938; 61078</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28398; 51958</t>
+          <t>27239; 52436</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16876; 37808</t>
+          <t>17373; 38974</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37445; 55677</t>
+          <t>41938; 61078</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29003</t>
+          <t>32311</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2131,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>15206; 37144</t>
+          <t>16012; 37634</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1343; 14208</t>
+          <t>1361; 12431</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22590; 37081</t>
+          <t>24578; 40283</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15206; 37144</t>
+          <t>16012; 37634</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1343; 14208</t>
+          <t>1361; 12431</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22590; 37081</t>
+          <t>24578; 40283</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
     </row>
@@ -2249,32 +2249,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>601929; 701351</t>
+          <t>610767; 709432</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>390425; 470981</t>
+          <t>393932; 471432</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>403168; 503641</t>
+          <t>477218; 548651</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>601929; 701351</t>
+          <t>610767; 709432</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>390425; 470981</t>
+          <t>393932; 471432</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>403168; 503641</t>
+          <t>477218; 548651</t>
         </is>
       </c>
     </row>
